--- a/output/pdf_financials_xlsx/NLR.xlsx
+++ b/output/pdf_financials_xlsx/NLR.xlsx
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.214998</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.214998</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.345298</v>
       </c>
     </row>
     <row r="93">
@@ -2361,13 +2361,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>-1.702114</v>
+        <v>-1.728289</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.002861</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>1.561587</v>
+        <v>1.525302</v>
       </c>
     </row>
     <row r="119">
@@ -3000,7 +3000,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>1.214998</v>
       </c>
@@ -3490,7 +3494,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -4089,7 +4097,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
         <v>-0.026175</v>
       </c>

--- a/output/pdf_financials_xlsx/NLR.xlsx
+++ b/output/pdf_financials_xlsx/NLR.xlsx
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.024183</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.004386</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.001052</v>
       </c>
     </row>
     <row r="35">
@@ -1010,13 +1010,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.78</v>
+        <v>0.804183</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.465</v>
+        <v>0.469386</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.001052</v>
       </c>
     </row>
     <row r="37">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.07625</v>
+        <v>0.052067</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.005173</v>
+        <v>0.000787</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.003152</v>
+        <v>0.0021</v>
       </c>
     </row>
     <row r="49">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/NLR.xlsx
+++ b/output/pdf_financials_xlsx/NLR.xlsx
@@ -1524,13 +1524,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0859</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.09150700000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.108739</v>
       </c>
     </row>
     <row r="68">
@@ -3591,7 +3591,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
